--- a/data/processed/mental_issue_rates.xlsx
+++ b/data/processed/mental_issue_rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MisLocalFiles\Github\HBSC\data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA3F4CD9-A80F-41AE-B4D0-396BE7933C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{DFA1DA6D-BF4F-4225-8815-94C9EEA9D922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61829032-8DD2-4ACE-9769-BB57544F05E6}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="55">
   <si>
     <t>continent</t>
   </si>
@@ -182,6 +182,9 @@
   </si>
   <si>
     <t>option by area</t>
+  </si>
+  <si>
+    <t>UK (4)</t>
   </si>
 </sst>
 </file>
@@ -690,7 +693,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
@@ -700,6 +703,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="9"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -1076,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A120B0-54BC-449B-8DD4-4D37C5F03F6B}">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
@@ -1084,35 +1093,34 @@
     <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
@@ -1124,11 +1132,14 @@
       <c r="E2" s="1">
         <v>0.26262988176280899</v>
       </c>
-      <c r="G2" s="6">
+      <c r="F2" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1144,8 +1155,11 @@
       <c r="E3" s="1">
         <v>0.151822796492847</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1161,8 +1175,11 @@
       <c r="E4" s="1">
         <v>0.30237467018469599</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1178,8 +1195,11 @@
       <c r="E5" s="1">
         <v>0.224735322425409</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1195,8 +1215,11 @@
       <c r="E6" s="1">
         <v>0.358827911596722</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1212,11 +1235,11 @@
       <c r="E7" s="1">
         <v>0.52774566473988405</v>
       </c>
-      <c r="G7" s="6">
+      <c r="F7" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1233,7 +1256,7 @@
         <v>0.27158135981665299</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1250,7 +1273,7 @@
         <v>0.27701729106628198</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1267,7 +1290,7 @@
         <v>0.262484394506866</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1283,11 +1306,11 @@
       <c r="E11" s="1">
         <v>0.328783621035728</v>
       </c>
-      <c r="G11" s="6">
+      <c r="F11" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1304,7 +1327,7 @@
         <v>0.22865971417535699</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1321,7 +1344,7 @@
         <v>0.32917820867959302</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1337,11 +1360,11 @@
       <c r="E14" s="1">
         <v>0.375494071146245</v>
       </c>
-      <c r="G14" s="6">
+      <c r="F14" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -1358,7 +1381,7 @@
         <v>0.30647024841132198</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1375,7 +1398,7 @@
         <v>0.24787052810902799</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1392,7 +1415,7 @@
         <v>0.25350520126639497</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1408,8 +1431,11 @@
       <c r="E18" s="1">
         <v>0.28405315614617899</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F18" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -1426,7 +1452,7 @@
         <v>0.24410029498524999</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -1443,7 +1469,7 @@
         <v>0.17791411042944699</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -1459,8 +1485,11 @@
       <c r="E21" s="1">
         <v>0.26384976525821502</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>16</v>
       </c>
@@ -1477,7 +1506,7 @@
         <v>0.32865048957002901</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1493,8 +1522,11 @@
       <c r="E23" s="1">
         <v>0.288794627076705</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F23" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -1511,7 +1543,7 @@
         <v>0.25237191650853802</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -1528,7 +1560,7 @@
         <v>0.229711141678129</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -1544,11 +1576,11 @@
       <c r="E26" s="1">
         <v>0.36252019386106599</v>
       </c>
-      <c r="G26" s="6">
+      <c r="F26" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -1564,11 +1596,11 @@
       <c r="E27" s="1">
         <v>0.42210386151797602</v>
       </c>
-      <c r="G27" s="6">
+      <c r="F27" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -1585,7 +1617,7 @@
         <v>0.340425531914893</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -1602,7 +1634,7 @@
         <v>0.24318869828456099</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -1619,7 +1651,7 @@
         <v>0.237966884867154</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -1636,7 +1668,7 @@
         <v>0.224107368954165</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -1653,7 +1685,7 @@
         <v>0.18620455317703</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -1670,7 +1702,7 @@
         <v>0.21590909090909</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -1687,7 +1719,7 @@
         <v>0.20886524822694999</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -1703,11 +1735,11 @@
       <c r="E35" s="1">
         <v>0.31528662420382098</v>
       </c>
-      <c r="G35" s="6">
+      <c r="F35" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>16</v>
       </c>
@@ -1723,11 +1755,11 @@
       <c r="E36" s="1">
         <v>0.30387288977159799</v>
       </c>
-      <c r="G36" s="6">
+      <c r="F36" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -1744,7 +1776,7 @@
         <v>0.17582417582417501</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -1760,11 +1792,11 @@
       <c r="E38" s="1">
         <v>0.280240073868882</v>
       </c>
-      <c r="G38" s="6">
+      <c r="F38" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>16</v>
       </c>
